--- a/output/topology_excel/7686.xlsx
+++ b/output/topology_excel/7686.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>281953</v>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>33075</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>281953</v>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>266</v>
       </c>
       <c r="F3" t="n">
-        <v>33075</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>266</v>
-      </c>
-      <c r="J3" t="n">
         <v>172</v>
       </c>
     </row>

--- a/output/topology_excel/7686.xlsx
+++ b/output/topology_excel/7686.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
         </is>
       </c>
     </row>
@@ -481,6 +501,10 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -495,13 +519,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="F3" t="n">
-        <v>172</v>
+        <v>28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>251</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
